--- a/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
+++ b/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1868,6 +1868,266 @@
       <c r="J25" s="25" t="inlineStr">
         <is>
           <t>偿付能力信息|风险管理|监管指标</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>B013</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>业务规模指标</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>责任保险保费</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>责任险保费|责任保险保费收入|责任险保费收入|liability insurance premium</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>责任保险保费收入|责任险保费收入|责任保险原保险保费收入|责任险原保险保费收入|责任保险业务保费收入|责任险业务保费收入|责任保险保费|责任险保费|责任保险|责任险|其他责任保险|责任保险业务|liability insurance premium|責任保險保費收入|責任險保費收入</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>责任保险业务保费收入。</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>按责任保险业务披露的保费金额提取；如披露单位为亿元，统一换算为百万元；不得提取同比增长率或变化百分点。</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>经营情况分析|业务结构|分部信息|保费收入公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B014</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>业务规模指标</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>意外伤害保险保费</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>意外险保费|意外伤害险保费|accident insurance premium</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>意外伤害保险保费收入|意外险保费收入|意外伤害险保费收入|意外伤害保险原保险保费收入|意外险原保险保费收入|意外伤害保险业务保费收入|意外险业务保费收入|意外伤害保险保费|意外险保费|意外伤害保险|意外险|意外伤害险|意外险业务|accident insurance premium|意外傷害保險保費收入|意外險保費收入</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>意外伤害保险业务保费收入。</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>按意外伤害保险业务披露的保费金额提取；如披露单位为亿元，统一换算为百万元；不得提取同比增长率或变化百分点。</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>经营情况分析|业务结构|分部信息|保费收入公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B015</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>业务规模指标</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>企财险保费</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>企业财产保险保费|企业财产险保费|commercial property insurance premium</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>企财险保费收入|企业财产保险保费收入|企业财产险保费收入|企财险原保险保费收入|企业财产保险原保险保费收入|企财险业务保费收入|企业财产保险业务保费收入|企财险保费|企业财产保险保费|企财险|企业财产保险|企业财产险|企财险业务|commercial property insurance premium|企業財產保險保費收入|企財險保費收入</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>企业财产保险业务保费收入。</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>按企业财产保险业务披露的保费金额提取；如披露单位为亿元，统一换算为百万元；不得提取同比增长率或变化百分点。</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>经营情况分析|业务结构|分部信息|保费收入公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B016</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>业务规模指标</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>保证保险保费</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>保证险保费|guarantee insurance premium</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>保证保险保费收入|保证险保费收入|保证保险原保险保费收入|保证险原保险保费收入|保证保险业务保费收入|保证险业务保费收入|保证保险保费|保证险保费|保证保险|保证险|保证保险业务|guarantee insurance premium|保證保險保費收入|保證險保費收入</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>保证保险业务保费收入。</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>按保证保险业务披露的保费金额提取；如披露单位为亿元，统一换算为百万元；不得提取同比增长率或变化百分点。</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>经营情况分析|业务结构|分部信息|保费收入公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B017</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>业务规模指标</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>货物运输保险保费</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>货运险保费|货物运输险保费|cargo transportation insurance premium</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>货物运输保险保费收入|货运险保费收入|货物运输险保费收入|货物运输保险原保险保费收入|货运险原保险保费收入|货物运输保险业务保费收入|货运险业务保费收入|货物运输保险保费|货运险保费|货物运输保险|货运险|货物运输险|货运险业务|cargo transportation insurance premium|貨物運輸保險保費收入|貨運險保費收入</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>货物运输保险业务保费收入。</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>按货物运输保险业务披露的保费金额提取；如披露单位为亿元，统一换算为百万元；不得提取同比增长率或变化百分点。</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>经营情况分析|业务结构|分部信息|保费收入公告</t>
         </is>
       </c>
     </row>

--- a/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
+++ b/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>责任保险保费收入|责任险保费收入|责任保险原保险保费收入|责任险原保险保费收入|责任保险业务保费收入|责任险业务保费收入|责任保险保费|责任险保费|责任保险|责任险|其他责任保险|责任保险业务|liability insurance premium|責任保險保費收入|責任險保費收入</t>
+          <t>责任保险保费收入|责任险保费收入|责任保险原保险保费收入|责任险原保险保费收入|责任保险业务保费收入|责任险业务保费收入|责任保险保费|责任险保费|责任保险|责任险|其他责任保险|责任保险业务|liability insurance premium|責任保險保費收入|責任險保費收入|責任保險|責任險|責任保險保費|責任險保費|責任保險業務|liability insurance</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>意外伤害保险保费收入|意外险保费收入|意外伤害险保费收入|意外伤害保险原保险保费收入|意外险原保险保费收入|意外伤害保险业务保费收入|意外险业务保费收入|意外伤害保险保费|意外险保费|意外伤害保险|意外险|意外伤害险|意外险业务|accident insurance premium|意外傷害保險保費收入|意外險保費收入</t>
+          <t>意外伤害保险保费收入|意外险保费收入|意外伤害险保费收入|意外伤害保险原保险保费收入|意外险原保险保费收入|意外伤害保险业务保费收入|意外险业务保费收入|意外伤害保险保费|意外险保费|意外伤害保险|意外险|意外伤害险|意外险业务|accident insurance premium|意外傷害保險保費收入|意外險保費收入|意外伤害|意外傷害|意外伤害保险业务|意外傷害保險業務|意外伤害及健康保险|意外傷害及健康險|意外健康险|意外健康險</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>企财险保费收入|企业财产保险保费收入|企业财产险保费收入|企财险原保险保费收入|企业财产保险原保险保费收入|企财险业务保费收入|企业财产保险业务保费收入|企财险保费|企业财产保险保费|企财险|企业财产保险|企业财产险|企财险业务|commercial property insurance premium|企業財產保險保費收入|企財險保費收入</t>
+          <t>企财险保费收入|企业财产保险保费收入|企业财产险保费收入|企财险原保险保费收入|企业财产保险原保险保费收入|企财险业务保费收入|企业财产保险业务保费收入|企财险保费|企业财产保险保费|企财险|企业财产保险|企业财产险|企财险业务|commercial property insurance premium|企業財產保險保費收入|企財險保費收入|企業財產保險|企業財產險|企業財產保險保費|企財險|企財險保費</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>保证保险保费收入|保证险保费收入|保证保险原保险保费收入|保证险原保险保费收入|保证保险业务保费收入|保证险业务保费收入|保证保险保费|保证险保费|保证保险|保证险|保证保险业务|guarantee insurance premium|保證保險保費收入|保證險保費收入</t>
+          <t>保证保险保费收入|保证险保费收入|保证保险原保险保费收入|保证险原保险保费收入|保证保险业务保费收入|保证险业务保费收入|保证保险保费|保证险保费|保证保险|保证险|保证保险业务|guarantee insurance premium|保證保險保費收入|保證險保費收入|保證保險|保證險|保證保險保費|保證險保費</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>货物运输保险保费收入|货运险保费收入|货物运输险保费收入|货物运输保险原保险保费收入|货运险原保险保费收入|货物运输保险业务保费收入|货运险业务保费收入|货物运输保险保费|货运险保费|货物运输保险|货运险|货物运输险|货运险业务|cargo transportation insurance premium|貨物運輸保險保費收入|貨運險保費收入</t>
+          <t>货物运输保险保费收入|货运险保费收入|货物运输险保费收入|货物运输保险原保险保费收入|货运险原保险保费收入|货物运输保险业务保费收入|货运险业务保费收入|货物运输保险保费|货运险保费|货物运输保险|货运险|货物运输险|货运险业务|cargo transportation insurance premium|貨物運輸保險保費收入|貨運險保費收入|貨物運輸保險|貨運險|貨物運輸險|貨物運輸保險保費|貨運險保費</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">

--- a/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
+++ b/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>产险实现净利润|财险实现净利润|财产险实现净利润|财产保险实现净利润|产险净利润|财险净利润|财产险净利润|财产保险净利润|财产保险业务净利润|财产险业务净利润|税后利润|net profit|净利润</t>
+          <t>产险实现净利润|财险实现净利润|财产险实现净利润|财产保险实现净利润|产险净利润|财险净利润|财产险净利润|财产保险净利润|财产保险业务净利润|财产险业务净利润|税后利润|net profit|净利润|淨溢利|溢利|歸屬於母公司股東的淨溢利|淨利潤</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>承保利润|保险服务业绩|underwriting result|承保经营利润|承保盈利|承保业绩|underwriting profit|underwriting income|承保利潤|underwriting profitability</t>
+          <t>承保利润|保险服务业绩|underwriting result|承保经营利润|承保盈利|承保业绩|underwriting profit|underwriting income|承保利潤|underwriting profitability|承保溢利|承保溢利/(虧損)|承保溢利(虧損)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>车险综合成本率|机动车辆保险综合成本率|motor COR|车险承保综合成本率|机动车辆险综合成本率|机动车辆险承保综合成本率|机动车辆保险承保综合成本率|motor combined ratio|車險綜合成本率</t>
+          <t>车险综合成本率|机动车辆保险综合成本率|motor COR|车险承保综合成本率|机动车辆险综合成本率|机动车辆险承保综合成本率|机动车辆保险承保综合成本率|motor combined ratio|車險綜合成本率|汽車生態綜合成本率|汽车生态综合成本率</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>原保险保费收入|原保费|保费收入|GWP|原保险保费|原保险保费收入合计|保险业务收入|保险业务收入合计|gross written premium|gross written premiums|原保險保費收入|保費收入</t>
+          <t>原保险保费收入|原保费|保费收入|GWP|原保险保费|原保险保费收入合计|保险业务收入|保险业务收入合计|gross written premium|gross written premiums|原保險保費收入|保費收入|總保費|总保费|保费总额</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>车险保费收入|机动车辆保险|motor insurance|车险原保险保费收入|车险原保费收入|车险保费|机动车辆险保费收入|机动车辆险原保险保费收入|机动车辆保险保费收入|机动车辆保险原保险保费收入|motor premiums|motor insurance premiums|机动车辆险</t>
+          <t>车险保费收入|机动车辆保险|motor insurance|车险原保险保费收入|车险原保费收入|车险保费|机动车辆险保费收入|机动车辆险原保险保费收入|机动车辆保险保费收入|机动车辆保险原保险保费收入|motor premiums|motor insurance premiums|机动车辆险|汽車生態總保費|車險總保費|汽车生态总保费|车险总保费</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>健康险|健康保险|health insurance|健康险保费|健康保险保费|健康险保费收入|健康保险保费收入|健康险原保险保费收入|健康保险原保险保费收入|health insurance premiums|健康險|長期健康險|短期健康險</t>
+          <t>健康险|健康保险|health insurance|健康险保费|健康保险保费|健康险保费收入|健康保险保费收入|健康险原保险保费收入|健康保险原保险保费收入|health insurance premiums|健康險|長期健康險|短期健康險|健康生態總保費|健康生态总保费</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>保费增长率|保费增速|保费同比增长|保费收入同比增长|原保费同比增长|原保险保费收入同比增长|原保险保费收入增长率|保费收入增长率|premium growth rate|保費增長率|保費增長</t>
+          <t>保费增长率|保费增速|保费同比增长|保费收入同比增长|原保费同比增长|原保险保费收入同比增长|原保险保费收入增长率|保费收入增长率|premium growth rate|保費增長率|保費增長|總保費同比|保費同比增長|同比變動|总保费同比|保费同比</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>机动车辆保险服务收入|车险保险服务收入|motor insurance service revenue|机动车辆险服务收入|机动车辆险保险服务收入|机动车辆保险业务保险服务收入|车险服务收入|車險保險服務收入</t>
+          <t>机动车辆保险服务收入|车险保险服务收入|motor insurance service revenue|机动车辆险服务收入|机动车辆险保险服务收入|机动车辆保险业务保险服务收入|车险服务收入|車險保險服務收入|汽車生態保險服務收入|汽车生态保险服务收入</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>新能源车险保费|新能源车保费|新能源车险业务保费|新能源车业务保费|新能源车险保费合计|新能源车保费合计|新能源车险保费收入|新能源车保费收入|新能源车险原保险保费收入|新能源车原保险保费收入|新能源车险原保费收入|新能源车原保费收入|新能源車險保費|新能源車保費|新能源車險業務保費|新能源車業務保費|new energy vehicle premiums|新能源汽车保险保费|新能源车险原保费</t>
+          <t>新能源车险保费|新能源车保费|新能源车险业务保费|新能源车业务保费|新能源车险保费合计|新能源车保费合计|新能源车险保费收入|新能源车保费收入|新能源车险原保险保费收入|新能源车原保险保费收入|新能源车险原保费收入|新能源车原保费收入|新能源車險保費|新能源車保費|新能源車險業務保費|新能源車業務保費|new energy vehicle premiums|新能源汽车保险保费|新能源车险原保费|新能源車險總保費|新能源車險佔比|新能源車險保費佔比|新能源车险总保费|新能源车险占比</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>按年报披露的'新能源车险/新能源汽车保险'保费提取;若未单独披露该险种保费,则不提取,不得用整体车险保费代替。</t>
+          <t>按年报披露的'新能源车险/新能源汽车保险'保费提取;若未单独披露绝对金额,但披露了占车险保费比例或同比增速,则提取比例/增速并注明口径;严禁用整体车险保费代替。</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">

--- a/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
+++ b/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
@@ -1574,7 +1574,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>机动车辆保险服务收入|车险保险服务收入|motor insurance service revenue|机动车辆险服务收入|机动车辆险保险服务收入|机动车辆保险业务保险服务收入|车险服务收入|車險保險服務收入|汽車生態保險服務收入|汽车生态保险服务收入</t>
+          <t>机动车辆保险服务收入|车险保险服务收入|motor insurance service revenue|机动车辆险服务收入|机动车辆险保险服务收入|机动车辆保险业务保险服务收入|车险服务收入|車險保險服務收入|汽車生態保險服務收入|汽车生态保险服务收入|汽車保險保險服務收入|汽车保险保险服务收入</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">

--- a/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
+++ b/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
@@ -4017,7 +4017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4212,6 +4212,40 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>business_scope</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>原始业务范围，保留 LLM 提取或人工修改后的原始描述。</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>太保产险单体（不含太平洋安信农险）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>business_scope_type</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>标准化口径分类，枚举：集团口径 / 财险口径 / 特殊财险口径；由业务口径标准化层生成，可在人工审核页面修正。</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>特殊财险口径</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
+++ b/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>健康险|健康保险|health insurance|健康险保费|健康保险保费|健康险保费收入|健康保险保费收入|健康险原保险保费收入|健康保险原保险保费收入|health insurance premiums|健康險|長期健康險|短期健康險|健康生態總保費|健康生态总保费</t>
+          <t>health insurance|健康险保费|健康保险保费|健康险保费收入|健康保险保费收入|健康险原保险保费收入|健康保险原保险保费收入|health insurance premiums|健康生態總保費|健康生态总保费</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>意外伤害保险保费收入|意外险保费收入|意外伤害险保费收入|意外伤害保险原保险保费收入|意外险原保险保费收入|意外伤害保险业务保费收入|意外险业务保费收入|意外伤害保险保费|意外险保费|意外伤害保险|意外险|意外伤害险|意外险业务|accident insurance premium|意外傷害保險保費收入|意外險保費收入|意外伤害|意外傷害|意外伤害保险业务|意外傷害保險業務|意外伤害及健康保险|意外傷害及健康險|意外健康险|意外健康險</t>
+          <t>意外伤害保险保费收入|意外险保费收入|意外伤害险保费收入|意外伤害保险原保险保费收入|意外险原保险保费收入|意外伤害保险业务保费收入|意外险业务保费收入|意外伤害保险保费|意外险保费|意外伤害保险|accident insurance premium|意外傷害保險保費收入|意外險保費收入|意外伤害保险业务|意外傷害保險業務</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3062,32 +3062,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>F011</t>
+          <t>B037</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>盈利能力指标</t>
+          <t>业务规模指标</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>车险承保利润</t>
+          <t>意健险保费收入</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>车险承保利润|机动车辆保险承保利润|motor underwriting profit</t>
+          <t>意外伤害及健康保险保费|意健险保费|accident &amp; health premiums</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>车险承保利润|机动车辆保险承保利润|车险业务承保利润|机动车辆保险业务承保利润|車險承保利潤|機動車輛保險承保利潤|車險業務承保利潤|機動車輛保險業務承保利潤|motor underwriting profit|车险承保经营利润|机动车辆保险承保经营利润</t>
+          <t>意外伤害及健康保险保费|意健险保费|意外伤害及健康保险业务保费|意健险业务保费|意外伤害及健康保险保费合计|意健险保费合计|意外伤害及健康保险保费收入|意健险保费收入|意外伤害及健康保险原保险保费收入|意健险原保险保费收入|意外伤害及健康保险原保费收入|意健险原保费收入|意外傷害及健康保險保費|意健險保費|意外傷害及健康保險業務保費|意健險業務保費|accident &amp; health premiums|意外傷害及健康保險保費|意健險保費</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>车险业务承保端形成的利润或亏损。</t>
+          <t>意外伤害及健康保险(意健险)业务合并披露口径的保费。仅当年报将意外伤害保险与健康保险按'意外伤害及健康保险/意健险'合并口径披露时提取;若两者分别披露,请分别提取到'意外险''健康险'指标下,本合并指标留空。</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+          <t>按'意外伤害及健康保险/意健险'合并口径提取;若分别披露意外伤害保险与健康保险,本指标留空。</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3114,32 +3114,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>B038</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>盈利能力指标</t>
+          <t>业务规模指标</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>非车险承保利润</t>
+          <t>意健险保险服务收入</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>非车险承保利润|非机动车辆保险承保利润|non-motor underwriting profit</t>
+          <t>意外伤害及健康保险保险服务收入|意健险保险服务收入|accident &amp; health insurance service revenue</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>非车险承保利润|非机动车辆保险承保利润|非车险业务承保利润|非机动车辆保险业务承保利润|非車險承保利潤|非機動車輛保險承保利潤|非車險業務承保利潤|非機動車輛保險業務承保利潤|non-motor underwriting profit|非车险承保经营利润|非机动车辆保险承保经营利润</t>
+          <t>意外伤害及健康保险保险服务收入|意健险保险服务收入|意外伤害及健康保险业务保险服务收入|意健险业务保险服务收入|意外伤害及健康保险保险服务收入合计|意健险保险服务收入合计|意外傷害及健康保險保險服務收入|意健險保險服務收入|意外傷害及健康保險業務保險服務收入|意健險業務保險服務收入|accident &amp; health insurance service revenue|意外傷害及健康保險保險服務收入|意健險保險服務收入</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>非车险业务承保端形成的利润或亏损。</t>
+          <t>意外伤害及健康保险(意健险)业务合并披露口径的保险服务收入。仅当年报将意外伤害保险与健康保险按'意外伤害及健康保险/意健险'合并口径披露时提取;若两者分别披露,请分别提取到'意外险''健康险'指标下,本合并指标留空。</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+          <t>按'意外伤害及健康保险/意健险'合并口径提取;若分别披露意外伤害保险与健康保险,本指标留空。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3166,32 +3166,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>B039</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>盈利能力指标</t>
+          <t>业务规模指标</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>农险承保利润</t>
+          <t>意健险保险服务费用</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>农业保险承保利润|农险承保利润|agricultural underwriting profit</t>
+          <t>意外伤害及健康保险保险服务费用|意健险保险服务费用|accident &amp; health insurance service expenses</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>农业保险承保利润|农险承保利润|农业保险业务承保利润|农险业务承保利润|農業保險承保利潤|農險承保利潤|農業保險業務承保利潤|農險業務承保利潤|agricultural underwriting profit|农业保险承保经营利润|农险承保经营利润</t>
+          <t>意外伤害及健康保险保险服务费用|意健险保险服务费用|意外伤害及健康保险业务保险服务费用|意健险业务保险服务费用|意外伤害及健康保险保险服务费用合计|意健险保险服务费用合计|意外傷害及健康保險保險服務費用|意健險保險服務費用|意外傷害及健康保險業務保險服務費用|意健險業務保險服務費用|accident &amp; health insurance service expenses|意外傷害及健康保險保險服務費用|意健險保險服務費用</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>农业保险业务承保端形成的利润或亏损。</t>
+          <t>意外伤害及健康保险(意健险)业务合并披露口径的保险服务费用。仅当年报将意外伤害保险与健康保险按'意外伤害及健康保险/意健险'合并口径披露时提取;若两者分别披露,请分别提取到'意外险''健康险'指标下,本合并指标留空。</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+          <t>按'意外伤害及健康保险/意健险'合并口径提取;若分别披露意外伤害保险与健康保险,本指标留空。</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3218,7 +3218,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F029</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3228,22 +3228,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>健康险承保利润</t>
+          <t>意健险承保利润</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>健康险承保利润|健康保险承保利润|health underwriting profit</t>
+          <t>意外伤害及健康保险承保利润|意健险承保利润</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>健康险承保利润|健康保险承保利润|健康险业务承保利润|健康保险业务承保利润|健康險承保利潤|健康保險承保利潤|健康險業務承保利潤|健康保險業務承保利潤|health underwriting profit|健康险承保经营利润|健康保险承保经营利润</t>
+          <t>意外伤害及健康保险承保利润|意健险承保利润|意外伤害及健康保险业务承保利润|意健险业务承保利润|意外傷害及健康保險承保利潤|意健險承保利潤|意外傷害及健康保險業務承保利潤|意健險業務承保利潤|accident &amp; health underwriting profit</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>健康险业务承保端形成的利润或亏损。</t>
+          <t>意外伤害及健康保险(意健险)业务合并披露口径的承保利润。仅当年报将意外伤害保险与健康保险按'意外伤害及健康保险/意健险'合并口径披露时提取;若两者分别披露,请分别提取到'意外险''健康险'指标下,本合并指标留空。</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+          <t>按'意外伤害及健康保险/意健险'合并口径提取;若分别披露意外伤害保险与健康保险,本指标留空。</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3270,47 +3270,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>F015</t>
+          <t>F030</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>盈利能力指标</t>
+          <t>承保质量指标</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>责任险承保利润</t>
+          <t>意健险综合成本率</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>责任保险承保利润|责任险承保利润|liability underwriting profit</t>
+          <t>意外伤害及健康保险综合成本率|意健险综合成本率|意健险COR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>责任保险承保利润|责任险承保利润|责任保险业务承保利润|责任险业务承保利润|責任保險承保利潤|責任險承保利潤|責任保險業務承保利潤|責任險業務承保利潤|liability underwriting profit|责任保险承保经营利润|责任险承保经营利润</t>
+          <t>意外伤害及健康保险综合成本率|意健险综合成本率|意外伤害及健康保险业务综合成本率|意健险业务综合成本率|意外傷害及健康保險綜合成本率|意健險綜合成本率|意外傷害及健康保險業務綜合成本率|意健險業務綜合成本率|accident &amp; health combined ratio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>责任保险业务承保端形成的利润或亏损。</t>
+          <t>意外伤害及健康保险(意健险)业务合并披露口径的综合成本率。仅当年报将意外伤害保险与健康保险按'意外伤害及健康保险/意健险'合并口径披露时提取;若两者分别披露,请分别提取到'意外险''健康险'指标下,本合并指标留空。</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percentage</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+          <t>按'意外伤害及健康保险/意健险'合并口径提取;若分别披露意外伤害保险与健康保险,本指标留空。</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3322,7 +3322,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F011</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>意外险承保利润</t>
+          <t>车险承保利润</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>意外伤害保险承保利润|意外险承保利润|accident underwriting profit</t>
+          <t>车险承保利润|机动车辆保险承保利润|motor underwriting profit</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>意外伤害保险承保利润|意外险承保利润|意外伤害保险业务承保利润|意外险业务承保利润|意外傷害保險承保利潤|意外險承保利潤|意外傷害保險業務承保利潤|意外險業務承保利潤|accident underwriting profit|意外伤害保险承保经营利润|意外险承保经营利润</t>
+          <t>车险承保利润|机动车辆保险承保利润|车险业务承保利润|机动车辆保险业务承保利润|車險承保利潤|機動車輛保險承保利潤|車險業務承保利潤|機動車輛保險業務承保利潤|motor underwriting profit|车险承保经营利润|机动车辆保险承保经营利润</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>意外伤害保险业务承保端形成的利润或亏损。</t>
+          <t>车险业务承保端形成的利润或亏损。</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3374,7 +3374,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>F017</t>
+          <t>F012</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3384,22 +3384,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>企财险承保利润</t>
+          <t>非车险承保利润</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>企业财产保险承保利润|企财险承保利润|commercial property underwriting profit</t>
+          <t>非车险承保利润|非机动车辆保险承保利润|non-motor underwriting profit</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>企业财产保险承保利润|企财险承保利润|企业财产保险业务承保利润|企财险业务承保利润|企業財產保險承保利潤|企財險承保利潤|企業財產保險業務承保利潤|企財險業務承保利潤|commercial property underwriting profit|企业财产保险承保经营利润|企财险承保经营利润</t>
+          <t>非车险承保利润|非机动车辆保险承保利润|非车险业务承保利润|非机动车辆保险业务承保利润|非車險承保利潤|非機動車輛保險承保利潤|非車險業務承保利潤|非機動車輛保險業務承保利潤|non-motor underwriting profit|非车险承保经营利润|非机动车辆保险承保经营利润</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>企业财产保险业务承保端形成的利润或亏损。</t>
+          <t>非车险业务承保端形成的利润或亏损。</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3426,7 +3426,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>F018</t>
+          <t>F013</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3436,22 +3436,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>保证险承保利润</t>
+          <t>农险承保利润</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>保证保险承保利润|保证险承保利润|guarantee underwriting profit</t>
+          <t>农业保险承保利润|农险承保利润|agricultural underwriting profit</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>保证保险承保利润|保证险承保利润|保证保险业务承保利润|保证险业务承保利润|保證保險承保利潤|保證險承保利潤|保證保險業務承保利潤|保證險業務承保利潤|guarantee underwriting profit|保证保险承保经营利润|保证险承保经营利润</t>
+          <t>农业保险承保利润|农险承保利润|农业保险业务承保利润|农险业务承保利润|農業保險承保利潤|農險承保利潤|農業保險業務承保利潤|農險業務承保利潤|agricultural underwriting profit|农业保险承保经营利润|农险承保经营利润</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>保证保险业务承保端形成的利润或亏损。</t>
+          <t>农业保险业务承保端形成的利润或亏损。</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3478,7 +3478,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F014</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3488,22 +3488,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>货运险承保利润</t>
+          <t>健康险承保利润</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>货物运输保险承保利润|货运险承保利润|cargo transportation underwriting profit</t>
+          <t>健康险承保利润|健康保险承保利润|health underwriting profit</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>货物运输保险承保利润|货运险承保利润|货物运输保险业务承保利润|货运险业务承保利润|貨物運輸保險承保利潤|貨運險承保利潤|貨物運輸保險業務承保利潤|貨運險業務承保利潤|cargo transportation underwriting profit|货物运输保险承保经营利润|货运险承保经营利润</t>
+          <t>健康险承保利润|健康保险承保利润|健康险业务承保利润|健康保险业务承保利润|健康險承保利潤|健康保險承保利潤|健康險業務承保利潤|健康保險業務承保利潤|health underwriting profit|健康险承保经营利润|健康保险承保经营利润</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>货物运输保险业务承保端形成的利润或亏损。</t>
+          <t>健康险业务承保端形成的利润或亏损。</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3530,7 +3530,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>F020</t>
+          <t>F015</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3540,22 +3540,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>新能源车险承保利润</t>
+          <t>责任险承保利润</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>新能源车险承保利润|新能源车承保利润|new energy vehicle underwriting profit</t>
+          <t>责任保险承保利润|责任险承保利润|liability underwriting profit</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>新能源车险承保利润|新能源车承保利润|新能源车险业务承保利润|新能源车业务承保利润|新能源車險承保利潤|新能源車承保利潤|新能源車險業務承保利潤|新能源車業務承保利潤|new energy vehicle underwriting profit|新能源车险承保经营利润|新能源车承保经营利润</t>
+          <t>责任保险承保利润|责任险承保利润|责任保险业务承保利润|责任险业务承保利润|責任保險承保利潤|責任險承保利潤|責任保險業務承保利潤|責任險業務承保利潤|liability underwriting profit|责任保险承保经营利润|责任险承保经营利润</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>新能源车险业务承保端形成的利润或亏损。仅在公司披露新能源车险/新能源汽车保险相关承保利润时提取;未披露不得提取,严禁与整体车险承保利润混淆。</t>
+          <t>责任保险业务承保端形成的利润或亏损。</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>按年报分险种披露口径提取;新能源车险须单独披露,否则不得提取。</t>
+          <t>按年报分险种披露口径提取;未披露则不提取。</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3582,42 +3582,42 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F016</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>承保质量指标</t>
+          <t>盈利能力指标</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>农险综合成本率</t>
+          <t>意外险承保利润</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>农业保险综合成本率|农险综合成本率|agricultural combined ratio</t>
+          <t>意外伤害保险承保利润|意外险承保利润|accident underwriting profit</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>农业保险综合成本率|农险综合成本率|农业保险业务综合成本率|农险业务综合成本率|農業保險綜合成本率|農險綜合成本率|農業保險業務綜合成本率|農險業務綜合成本率|agricultural combined ratio|农业保险COR|农险COR|农业保险承保综合成本率|农险承保综合成本率</t>
+          <t>意外伤害保险承保利润|意外险承保利润|意外伤害保险业务承保利润|意外险业务承保利润|意外傷害保險承保利潤|意外險承保利潤|意外傷害保險業務承保利潤|意外險業務承保利潤|accident underwriting profit|意外伤害保险承保经营利润|意外险承保经营利润</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>农业保险业务综合成本率(COR)。</t>
+          <t>意外伤害保险业务承保端形成的利润或亏损。</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3634,42 +3634,42 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>F017</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>承保质量指标</t>
+          <t>盈利能力指标</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>健康险综合成本率</t>
+          <t>企财险承保利润</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>健康险综合成本率|健康保险综合成本率|health combined ratio</t>
+          <t>企业财产保险承保利润|企财险承保利润|commercial property underwriting profit</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>健康险综合成本率|健康保险综合成本率|健康险业务综合成本率|健康保险业务综合成本率|健康險綜合成本率|健康保險綜合成本率|健康險業務綜合成本率|健康保險業務綜合成本率|health combined ratio|健康险COR|健康保险COR|健康险承保综合成本率|健康保险承保综合成本率</t>
+          <t>企业财产保险承保利润|企财险承保利润|企业财产保险业务承保利润|企财险业务承保利润|企業財產保險承保利潤|企財險承保利潤|企業財產保險業務承保利潤|企財險業務承保利潤|commercial property underwriting profit|企业财产保险承保经营利润|企财险承保经营利润</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>健康险业务综合成本率(COR)。</t>
+          <t>企业财产保险业务承保端形成的利润或亏损。</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3686,42 +3686,42 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>F023</t>
+          <t>F018</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>承保质量指标</t>
+          <t>盈利能力指标</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>责任险综合成本率</t>
+          <t>保证险承保利润</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>责任保险综合成本率|责任险综合成本率|liability combined ratio</t>
+          <t>保证保险承保利润|保证险承保利润|guarantee underwriting profit</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>责任保险综合成本率|责任险综合成本率|责任保险业务综合成本率|责任险业务综合成本率|責任保險綜合成本率|責任險綜合成本率|責任保險業務綜合成本率|責任險業務綜合成本率|liability combined ratio|责任保险COR|责任险COR|责任保险承保综合成本率|责任险承保综合成本率</t>
+          <t>保证保险承保利润|保证险承保利润|保证保险业务承保利润|保证险业务承保利润|保證保險承保利潤|保證險承保利潤|保證保險業務承保利潤|保證險業務承保利潤|guarantee underwriting profit|保证保险承保经营利润|保证险承保经营利润</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>责任保险业务综合成本率(COR)。</t>
+          <t>保证保险业务承保端形成的利润或亏损。</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3738,42 +3738,42 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>F024</t>
+          <t>F019</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>承保质量指标</t>
+          <t>盈利能力指标</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>意外险综合成本率</t>
+          <t>货运险承保利润</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>意外伤害保险综合成本率|意外险综合成本率|accident combined ratio</t>
+          <t>货物运输保险承保利润|货运险承保利润|cargo transportation underwriting profit</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>意外伤害保险综合成本率|意外险综合成本率|意外伤害保险业务综合成本率|意外险业务综合成本率|意外傷害保險綜合成本率|意外險綜合成本率|意外傷害保險業務綜合成本率|意外險業務綜合成本率|accident combined ratio|意外伤害保险COR|意外险COR|意外伤害保险承保综合成本率|意外险承保综合成本率</t>
+          <t>货物运输保险承保利润|货运险承保利润|货物运输保险业务承保利润|货运险业务承保利润|貨物運輸保險承保利潤|貨運險承保利潤|貨物運輸保險業務承保利潤|貨運險業務承保利潤|cargo transportation underwriting profit|货物运输保险承保经营利润|货运险承保经营利润</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>意外伤害保险业务综合成本率(COR)。</t>
+          <t>货物运输保险业务承保端形成的利润或亏损。</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3790,47 +3790,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>F025</t>
+          <t>F020</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>承保质量指标</t>
+          <t>盈利能力指标</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>企财险综合成本率</t>
+          <t>新能源车险承保利润</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>企业财产保险综合成本率|企财险综合成本率|commercial property combined ratio</t>
+          <t>新能源车险承保利润|新能源车承保利润|new energy vehicle underwriting profit</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>企业财产保险综合成本率|企财险综合成本率|企业财产保险业务综合成本率|企财险业务综合成本率|企業財產保險綜合成本率|企財險綜合成本率|企業財產保險業務綜合成本率|企財險業務綜合成本率|commercial property combined ratio|企业财产保险COR|企财险COR|企业财产保险承保综合成本率|企财险承保综合成本率</t>
+          <t>新能源车险承保利润|新能源车承保利润|新能源车险业务承保利润|新能源车业务承保利润|新能源車險承保利潤|新能源車承保利潤|新能源車險業務承保利潤|新能源車業務承保利潤|new energy vehicle underwriting profit|新能源车险承保经营利润|新能源车承保经营利润</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>企业财产保险业务综合成本率(COR)。</t>
+          <t>新能源车险业务承保端形成的利润或亏损。仅在公司披露新能源车险/新能源汽车保险相关承保利润时提取;未披露不得提取,严禁与整体车险承保利润混淆。</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>百万元</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>percentage</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+          <t>按年报分险种披露口径提取;新能源车险须单独披露,否则不得提取。</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3842,7 +3842,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>F026</t>
+          <t>F021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3852,22 +3852,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>保证险综合成本率</t>
+          <t>农险综合成本率</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>保证保险综合成本率|保证险综合成本率|guarantee combined ratio</t>
+          <t>农业保险综合成本率|农险综合成本率|agricultural combined ratio</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>保证保险综合成本率|保证险综合成本率|保证保险业务综合成本率|保证险业务综合成本率|保證保險綜合成本率|保證險綜合成本率|保證保險業務綜合成本率|保證險業務綜合成本率|guarantee combined ratio|保证保险COR|保证险COR|保证保险承保综合成本率|保证险承保综合成本率</t>
+          <t>农业保险综合成本率|农险综合成本率|农业保险业务综合成本率|农险业务综合成本率|農業保險綜合成本率|農險綜合成本率|農業保險業務綜合成本率|農險業務綜合成本率|agricultural combined ratio|农业保险COR|农险COR|农业保险承保综合成本率|农险承保综合成本率</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>保证保险业务综合成本率(COR)。</t>
+          <t>农业保险业务综合成本率(COR)。</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>F027</t>
+          <t>F022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3904,22 +3904,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>货运险综合成本率</t>
+          <t>健康险综合成本率</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>货物运输保险综合成本率|货运险综合成本率|cargo transportation combined ratio</t>
+          <t>健康险综合成本率|健康保险综合成本率|health combined ratio</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>货物运输保险综合成本率|货运险综合成本率|货物运输保险业务综合成本率|货运险业务综合成本率|貨物運輸保險綜合成本率|貨運險綜合成本率|貨物運輸保險業務綜合成本率|貨運險業務綜合成本率|cargo transportation combined ratio|货物运输保险COR|货运险COR|货物运输保险承保综合成本率|货运险承保综合成本率</t>
+          <t>健康险综合成本率|健康保险综合成本率|健康险业务综合成本率|健康保险业务综合成本率|健康險綜合成本率|健康保險綜合成本率|健康險業務綜合成本率|健康保險業務綜合成本率|health combined ratio|健康险COR|健康保险COR|健康险承保综合成本率|健康保险承保综合成本率</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>货物运输保险业务综合成本率(COR)。</t>
+          <t>健康险业务综合成本率(COR)。</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3946,50 +3946,310 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>F023</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>承保质量指标</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>责任险综合成本率</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>责任保险综合成本率|责任险综合成本率|liability combined ratio</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>责任保险综合成本率|责任险综合成本率|责任保险业务综合成本率|责任险业务综合成本率|責任保險綜合成本率|責任險綜合成本率|責任保險業務綜合成本率|責任險業務綜合成本率|liability combined ratio|责任保险COR|责任险COR|责任保险承保综合成本率|责任险承保综合成本率</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>责任保险业务综合成本率(COR)。</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>经营情况分析|分部信息|主要险种经营信息|分险种信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>F024</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>承保质量指标</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>意外险综合成本率</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>意外伤害保险综合成本率|意外险综合成本率|accident combined ratio</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>意外伤害保险综合成本率|意外险综合成本率|意外伤害保险业务综合成本率|意外险业务综合成本率|意外傷害保險綜合成本率|意外險綜合成本率|意外傷害保險業務綜合成本率|意外險業務綜合成本率|accident combined ratio|意外伤害保险COR|意外险COR|意外伤害保险承保综合成本率|意外险承保综合成本率</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>意外伤害保险业务综合成本率(COR)。</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>经营情况分析|分部信息|主要险种经营信息|分险种信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>F025</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>承保质量指标</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>企财险综合成本率</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>企业财产保险综合成本率|企财险综合成本率|commercial property combined ratio</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>企业财产保险综合成本率|企财险综合成本率|企业财产保险业务综合成本率|企财险业务综合成本率|企業財產保險綜合成本率|企財險綜合成本率|企業財產保險業務綜合成本率|企財險業務綜合成本率|commercial property combined ratio|企业财产保险COR|企财险COR|企业财产保险承保综合成本率|企财险承保综合成本率</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>企业财产保险业务综合成本率(COR)。</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>经营情况分析|分部信息|主要险种经营信息|分险种信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>F026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>承保质量指标</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>保证险综合成本率</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>保证保险综合成本率|保证险综合成本率|guarantee combined ratio</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>保证保险综合成本率|保证险综合成本率|保证保险业务综合成本率|保证险业务综合成本率|保證保險綜合成本率|保證險綜合成本率|保證保險業務綜合成本率|保證險業務綜合成本率|guarantee combined ratio|保证保险COR|保证险COR|保证保险承保综合成本率|保证险承保综合成本率</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>保证保险业务综合成本率(COR)。</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>经营情况分析|分部信息|主要险种经营信息|分险种信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>F027</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>承保质量指标</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>货运险综合成本率</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>货物运输保险综合成本率|货运险综合成本率|cargo transportation combined ratio</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>货物运输保险综合成本率|货运险综合成本率|货物运输保险业务综合成本率|货运险业务综合成本率|貨物運輸保險綜合成本率|貨運險綜合成本率|貨物運輸保險業務綜合成本率|貨運險業務綜合成本率|cargo transportation combined ratio|货物运输保险COR|货运险COR|货物运输保险承保综合成本率|货运险承保综合成本率</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>货物运输保险业务综合成本率(COR)。</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>percentage</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>按年报分险种披露口径提取;未披露则不提取。</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>经营情况分析|分部信息|主要险种经营信息|分险种信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>F028</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>承保质量指标</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>新能源车险综合成本率</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>新能源车险综合成本率|新能源车综合成本率|new energy vehicle combined ratio</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>新能源车险综合成本率|新能源车综合成本率|新能源车险业务综合成本率|新能源车业务综合成本率|新能源車險綜合成本率|新能源車綜合成本率|新能源車險業務綜合成本率|新能源車業務綜合成本率|new energy vehicle combined ratio|新能源车险COR|新能源车COR|新能源车险承保综合成本率|新能源车承保综合成本率</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>新能源车险业务综合成本率(COR)。仅在公司披露新能源车险/新能源汽车保险综合成本率时提取;未披露不得提取,严禁与整体车险综合成本率混淆。</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>按年报分险种披露口径提取;新能源车险须单独披露,否则不得提取。</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>经营情况分析|分部信息|主要险种经营信息|分险种信息</t>
         </is>

--- a/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
+++ b/agents/zd-agent0811/indicator/indicator_dictionary.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>车险综合成本率|机动车辆保险综合成本率|motor COR|车险承保综合成本率|机动车辆险综合成本率|机动车辆险承保综合成本率|机动车辆保险承保综合成本率|motor combined ratio|車險綜合成本率|汽車生態綜合成本率|汽车生态综合成本率</t>
+          <t>车险综合成本率|机动车辆保险综合成本率|motor COR|车险承保综合成本率|机动车辆险综合成本率|机动车辆险承保综合成本率|机动车辆保险承保综合成本率|motor combined ratio|車險綜合成本率|汽車生態綜合成本率|汽车生态综合成本率|機動車輛險綜合成本率|機動車輛保險綜合成本率|機動車輛險承保綜合成本率|機動車輛保險承保綜合成本率</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>车险保费收入|机动车辆保险|motor insurance|车险原保险保费收入|车险原保费收入|车险保费|机动车辆险保费收入|机动车辆险原保险保费收入|机动车辆保险保费收入|机动车辆保险原保险保费收入|motor premiums|motor insurance premiums|机动车辆险|汽車生態總保費|車險總保費|汽车生态总保费|车险总保费</t>
+          <t>车险保费收入|机动车辆保险|motor insurance|车险原保险保费收入|车险原保费收入|车险保费|机动车辆险保费收入|机动车辆险原保险保费收入|机动车辆保险保费收入|机动车辆保险原保险保费收入|motor premiums|motor insurance premiums|机动车辆险|汽車生態總保費|車險總保費|汽车生态总保费|车险总保费|機動車輛險保費收入|機動車輛保險保費收入|機動車輛險原保險保費收入|機動車輛保險原保險保費收入|機動車輛險原保費收入|機動車輛保險原保費收入</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>机动车辆保险服务收入|车险保险服务收入|motor insurance service revenue|机动车辆险服务收入|机动车辆险保险服务收入|机动车辆保险业务保险服务收入|车险服务收入|車險保險服務收入|汽車生態保險服務收入|汽车生态保险服务收入|汽車保險保險服務收入|汽车保险保险服务收入</t>
+          <t>机动车辆保险服务收入|车险保险服务收入|motor insurance service revenue|机动车辆险服务收入|机动车辆险保险服务收入|机动车辆保险业务保险服务收入|车险服务收入|車險保險服務收入|汽車生態保險服務收入|汽车生态保险服务收入|汽車保險保險服務收入|汽车保险保险服务收入|機動車輛險保險服務收入|機動車輛保險保險服務收入|機動車輛險保險服務收入合計|機動車輛保險保險服務收入合計</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>货物运输保险保费收入|货运险保费收入|货物运输险保费收入|货物运输保险原保险保费收入|货运险原保险保费收入|货物运输保险业务保费收入|货运险业务保费收入|货物运输保险保费|货运险保费|货物运输保险|货运险|货物运输险|货运险业务|cargo transportation insurance premium|貨物運輸保險保費收入|貨運險保費收入|貨物運輸保險|貨運險|貨物運輸險|貨物運輸保險保費|貨運險保費</t>
+          <t>货物运输保险保费收入|货运险保费收入|货物运输险保费收入|货物运输保险原保险保费收入|货运险原保险保费收入|货物运输保险业务保费收入|货运险业务保费收入|货物运输保险保费|货运险保费|货物运输保险|货运险|货物运输险|货运险业务|cargo transportation insurance premium|貨物運輸保險保費收入|貨運險保費收入|貨物運輸保險|貨運險|貨物運輸險|貨物運輸保險保費|貨運險保費|貨物運輸險保費收入|貨物運輸險原保險保費收入|貨物運輸險原保費收入|貨物運輸險保費</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>车险保险服务费用|机动车辆保险保险服务费用|车险业务保险服务费用|机动车辆保险业务保险服务费用|车险保险服务费用合计|机动车辆保险保险服务费用合计|車險保險服務費用|機動車輛保險保險服務費用|車險業務保險服務費用|機動車輛保險業務保險服務費用|motor insurance service expenses</t>
+          <t>车险保险服务费用|车险业务保险服务费用|车险保险服务费用合计|机动车辆保险保险服务费用|机动车辆保险业务保险服务费用|机动车辆保险保险服务费用合计|机动车辆险保险服务费用|机动车辆险业务保险服务费用|机动车辆险保险服务费用合计|車險保險服務費用|車險业务保險服務費用|機動車輛保險保險服務費用|機動車輛保險业务保險服務費用|機動車輛險保險服務費用|機動車輛險业务保險服務費用|motor insurance service expenses</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>非车险保险服务费用|非机动车辆保险保险服务费用|非车险业务保险服务费用|非机动车辆保险业务保险服务费用|非车险保险服务费用合计|非机动车辆保险保险服务费用合计|非車險保險服務費用|非機動車輛保險保險服務費用|非車險業務保險服務費用|非機動車輛保險業務保險服務費用|non-motor insurance service expenses</t>
+          <t>非车险保险服务费用|非车险业务保险服务费用|非车险保险服务费用合计|非机动车辆保险保险服务费用|非机动车辆保险业务保险服务费用|非机动车辆保险保险服务费用合计|非机动车辆险保险服务费用|非机动车辆险业务保险服务费用|非机动车辆险保险服务费用合计|非車險保險服務費用|非車險业务保險服務費用|非機動車輛保險保險服務費用|非機動車輛保險业务保險服務費用|非機動車輛險保險服務費用|非機動車輛險业务保險服務費用|non-motor insurance service expenses</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>农业保险保险服务费用|农险保险服务费用|农业保险业务保险服务费用|农险业务保险服务费用|农业保险保险服务费用合计|农险保险服务费用合计|農業保險保險服務費用|農險保險服務費用|農業保險業務保險服務費用|農險業務保險服務費用|agricultural insurance service expenses</t>
+          <t>农业保险保险服务费用|农业保险业务保险服务费用|农业保险保险服务费用合计|农业险保险服务费用|农业险业务保险服务费用|农业险保险服务费用合计|农险保险服务费用|农险业务保险服务费用|农险保险服务费用合计|農業保險保險服務費用|農業保險业务保險服務費用|農業險保險服務費用|農業險业务保險服務費用|農險保險服務費用|農險业务保險服務費用|agricultural insurance service expenses</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>健康险保险服务费用|健康保险保险服务费用|健康险业务保险服务费用|健康保险业务保险服务费用|健康险保险服务费用合计|健康保险保险服务费用合计|健康險保險服務費用|健康保險保險服務費用|健康險業務保險服務費用|健康保險業務保險服務費用|health insurance service expenses</t>
+          <t>健康险保险服务费用|健康险业务保险服务费用|健康险保险服务费用合计|健康保险保险服务费用|健康保险业务保险服务费用|健康保险保险服务费用合计|健康险保险服务费用|健康险业务保险服务费用|健康险保险服务费用合计|健康險保險服務費用|健康險业务保險服務費用|健康保險保險服務費用|健康保險业务保險服務費用|健康險保險服務費用|健康險业务保險服務費用|health insurance service expenses</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>责任保险保险服务费用|责任险保险服务费用|责任保险业务保险服务费用|责任险业务保险服务费用|责任保险保险服务费用合计|责任险保险服务费用合计|責任保險保險服務費用|責任險保險服務費用|責任保險業務保險服務費用|責任險業務保險服務費用|liability insurance service expenses</t>
+          <t>责任保险保险服务费用|责任保险业务保险服务费用|责任保险保险服务费用合计|责任险保险服务费用|责任险业务保险服务费用|责任险保险服务费用合计|责任险保险服务费用|责任险业务保险服务费用|责任险保险服务费用合计|責任保險保險服務費用|責任保險业务保險服務費用|責任險保險服務費用|責任險业务保險服務費用|責任險保險服務費用|責任險业务保險服務費用|liability insurance service expenses</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>意外伤害保险保险服务费用|意外险保险服务费用|意外伤害保险业务保险服务费用|意外险业务保险服务费用|意外伤害保险保险服务费用合计|意外险保险服务费用合计|意外傷害保險保險服務費用|意外險保險服務費用|意外傷害保險業務保險服務費用|意外險業務保險服務費用|accident insurance service expenses</t>
+          <t>意外伤害保险保险服务费用|意外伤害保险业务保险服务费用|意外伤害保险保险服务费用合计|意外伤害险保险服务费用|意外伤害险业务保险服务费用|意外伤害险保险服务费用合计|意外险保险服务费用|意外险业务保险服务费用|意外险保险服务费用合计|意外傷害保險保險服務費用|意外傷害保險业务保險服務費用|意外傷害險保險服務費用|意外傷害險业务保險服務費用|意外險保險服務費用|意外險业务保險服務費用|accident insurance service expenses</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>企业财产保险保险服务费用|企财险保险服务费用|企业财产保险业务保险服务费用|企财险业务保险服务费用|企业财产保险保险服务费用合计|企财险保险服务费用合计|企業財產保險保險服務費用|企財險保險服務費用|企業財產保險業務保險服務費用|企財險業務保險服務費用|commercial property insurance service expenses</t>
+          <t>企业财产保险保险服务费用|企业财产保险业务保险服务费用|企业财产保险保险服务费用合计|企业财产险保险服务费用|企业财产险业务保险服务费用|企业财产险保险服务费用合计|企财险保险服务费用|企财险业务保险服务费用|企财险保险服务费用合计|企業財產保險保險服務費用|企業財產保險业务保險服務費用|企業財產險保險服務費用|企業財產險业务保險服務費用|企財險保險服務費用|企財險业务保險服務費用|commercial property insurance service expenses</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>保证保险保险服务费用|保证险保险服务费用|保证保险业务保险服务费用|保证险业务保险服务费用|保证保险保险服务费用合计|保证险保险服务费用合计|保證保險保險服務費用|保證險保險服務費用|保證保險業務保險服務費用|保證險業務保險服務費用|guarantee insurance service expenses</t>
+          <t>保证保险保险服务费用|保证保险业务保险服务费用|保证保险保险服务费用合计|保证险保险服务费用|保证险业务保险服务费用|保证险保险服务费用合计|保证险保险服务费用|保证险业务保险服务费用|保证险保险服务费用合计|保證保險保險服務費用|保證保險业务保險服務費用|保證險保險服務費用|保證險业务保險服務費用|保證險保險服務費用|保證險业务保險服務費用|guarantee insurance service expenses</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>货物运输保险保险服务费用|货运险保险服务费用|货物运输保险业务保险服务费用|货运险业务保险服务费用|货物运输保险保险服务费用合计|货运险保险服务费用合计|貨物運輸保險保險服務費用|貨運險保險服務費用|貨物運輸保險業務保險服務費用|貨運險業務保險服務費用|cargo transportation insurance service expenses</t>
+          <t>货物运输保险保险服务费用|货物运输保险业务保险服务费用|货物运输保险保险服务费用合计|货物运输险保险服务费用|货物运输险业务保险服务费用|货物运输险保险服务费用合计|货运险保险服务费用|货运险业务保险服务费用|货运险保险服务费用合计|貨物運輸保險保險服務費用|貨物運輸保險业务保險服務費用|貨物運輸險保險服務費用|貨物運輸險业务保險服務費用|貨運險保險服務費用|貨運險业务保險服務費用|cargo transportation insurance service expenses</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>新能源车险保险服务费用|新能源车保险服务费用|新能源车险业务保险服务费用|新能源车业务保险服务费用|新能源车险保险服务费用合计|新能源车保险服务费用合计|新能源車險保險服務費用|新能源車保險服務費用|新能源車險業務保險服務費用|新能源車業務保險服務費用|new energy vehicle insurance service expenses</t>
+          <t>新能源车险保险服务费用|新能源车险业务保险服务费用|新能源车险保险服务费用合计|新能源车保险服务费用|新能源车业务保险服务费用|新能源车保险服务费用合计|新能源車險保險服務費用|新能源車險业务保險服務費用|新能源車保險服務費用|新能源車业务保險服務費用|new energy vehicle insurance service expenses</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>农业保险保险服务收入|农险保险服务收入|农业保险业务保险服务收入|农险业务保险服务收入|农业保险保险服务收入合计|农险保险服务收入合计|農業保險保險服務收入|農險保險服務收入|農業保險業務保險服務收入|農險業務保險服務收入|agricultural insurance service revenue</t>
+          <t>农业保险保险服务收入|农业保险业务保险服务收入|农业保险保险服务收入合计|农业险保险服务收入|农业险业务保险服务收入|农业险保险服务收入合计|农险保险服务收入|农险业务保险服务收入|农险保险服务收入合计|農業保險保險服務收入|農業保險业务保險服務收入|農業險保險服務收入|農業險业务保險服務收入|農險保險服務收入|農險业务保險服務收入|agricultural insurance service revenue</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>健康险保险服务收入|健康保险保险服务收入|健康险业务保险服务收入|健康保险业务保险服务收入|健康险保险服务收入合计|健康保险保险服务收入合计|健康險保險服務收入|健康保險保險服務收入|健康險業務保險服務收入|健康保險業務保險服務收入|health insurance service revenue</t>
+          <t>健康险保险服务收入|健康险业务保险服务收入|健康险保险服务收入合计|健康保险保险服务收入|健康保险业务保险服务收入|健康保险保险服务收入合计|健康险保险服务收入|健康险业务保险服务收入|健康险保险服务收入合计|健康險保險服務收入|健康險业务保險服務收入|健康保險保險服務收入|健康保險业务保險服務收入|健康險保險服務收入|健康險业务保險服務收入|health insurance service revenue</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>责任保险保险服务收入|责任险保险服务收入|责任保险业务保险服务收入|责任险业务保险服务收入|责任保险保险服务收入合计|责任险保险服务收入合计|責任保險保險服務收入|責任險保險服務收入|責任保險業務保險服務收入|責任險業務保險服務收入|liability insurance service revenue</t>
+          <t>责任保险保险服务收入|责任保险业务保险服务收入|责任保险保险服务收入合计|责任险保险服务收入|责任险业务保险服务收入|责任险保险服务收入合计|责任险保险服务收入|责任险业务保险服务收入|责任险保险服务收入合计|責任保險保險服務收入|責任保險业务保險服務收入|責任險保險服務收入|責任險业务保險服務收入|責任險保險服務收入|責任險业务保險服務收入|liability insurance service revenue</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>意外伤害保险保险服务收入|意外险保险服务收入|意外伤害保险业务保险服务收入|意外险业务保险服务收入|意外伤害保险保险服务收入合计|意外险保险服务收入合计|意外傷害保險保險服務收入|意外險保險服務收入|意外傷害保險業務保險服務收入|意外險業務保險服務收入|accident insurance service revenue</t>
+          <t>意外伤害保险保险服务收入|意外伤害保险业务保险服务收入|意外伤害保险保险服务收入合计|意外伤害险保险服务收入|意外伤害险业务保险服务收入|意外伤害险保险服务收入合计|意外险保险服务收入|意外险业务保险服务收入|意外险保险服务收入合计|意外傷害保險保險服務收入|意外傷害保險业务保險服務收入|意外傷害險保險服務收入|意外傷害險业务保險服務收入|意外險保險服務收入|意外險业务保險服務收入|accident insurance service revenue</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>企业财产保险保险服务收入|企财险保险服务收入|企业财产保险业务保险服务收入|企财险业务保险服务收入|企业财产保险保险服务收入合计|企财险保险服务收入合计|企業財產保險保險服務收入|企財險保險服務收入|企業財產保險業務保險服務收入|企財險業務保險服務收入|commercial property insurance service revenue</t>
+          <t>企业财产保险保险服务收入|企业财产保险业务保险服务收入|企业财产保险保险服务收入合计|企业财产险保险服务收入|企业财产险业务保险服务收入|企业财产险保险服务收入合计|企财险保险服务收入|企财险业务保险服务收入|企财险保险服务收入合计|企業財產保險保險服務收入|企業財產保險业务保險服務收入|企業財產險保險服務收入|企業財產險业务保險服務收入|企財險保險服務收入|企財險业务保險服務收入|commercial property insurance service revenue</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>保证保险保险服务收入|保证险保险服务收入|保证保险业务保险服务收入|保证险业务保险服务收入|保证保险保险服务收入合计|保证险保险服务收入合计|保證保險保險服務收入|保證險保險服務收入|保證保險業務保險服務收入|保證險業務保險服務收入|guarantee insurance service revenue</t>
+          <t>保证保险保险服务收入|保证保险业务保险服务收入|保证保险保险服务收入合计|保证险保险服务收入|保证险业务保险服务收入|保证险保险服务收入合计|保证险保险服务收入|保证险业务保险服务收入|保证险保险服务收入合计|保證保險保險服務收入|保證保險业务保險服務收入|保證險保險服務收入|保證險业务保險服務收入|保證險保險服務收入|保證險业务保險服務收入|guarantee insurance service revenue</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>货物运输保险保险服务收入|货运险保险服务收入|货物运输保险业务保险服务收入|货运险业务保险服务收入|货物运输保险保险服务收入合计|货运险保险服务收入合计|貨物運輸保險保險服務收入|貨運險保險服務收入|貨物運輸保險業務保險服務收入|貨運險業務保險服務收入|cargo transportation insurance service revenue</t>
+          <t>货物运输保险保险服务收入|货物运输保险业务保险服务收入|货物运输保险保险服务收入合计|货物运输险保险服务收入|货物运输险业务保险服务收入|货物运输险保险服务收入合计|货运险保险服务收入|货运险业务保险服务收入|货运险保险服务收入合计|貨物運輸保險保險服務收入|貨物運輸保險业务保險服務收入|貨物運輸險保險服務收入|貨物運輸險业务保險服務收入|貨運險保險服務收入|貨運險业务保險服務收入|cargo transportation insurance service revenue</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>新能源车险保险服务收入|新能源车保险服务收入|新能源车险业务保险服务收入|新能源车业务保险服务收入|新能源车险保险服务收入合计|新能源车保险服务收入合计|新能源車險保險服務收入|新能源車保險服務收入|新能源車險業務保險服務收入|新能源車業務保險服務收入|new energy vehicle insurance service revenue</t>
+          <t>新能源车险保险服务收入|新能源车险业务保险服务收入|新能源车险保险服务收入合计|新能源车保险服务收入|新能源车业务保险服务收入|新能源车保险服务收入合计|新能源車險保險服務收入|新能源車險业务保險服務收入|新能源車保險服務收入|新能源車业务保險服務收入|new energy vehicle insurance service revenue</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>新能源车险保费|新能源车保费|新能源车险业务保费|新能源车业务保费|新能源车险保费合计|新能源车保费合计|新能源车险保费收入|新能源车保费收入|新能源车险原保险保费收入|新能源车原保险保费收入|新能源车险原保费收入|新能源车原保费收入|新能源車險保費|新能源車保費|新能源車險業務保費|新能源車業務保費|new energy vehicle premiums|新能源汽车保险保费|新能源车险原保费|新能源車險總保費|新能源車險佔比|新能源車險保費佔比|新能源车险总保费|新能源车险占比</t>
+          <t>新能源车险保费|新能源车险业务保费|新能源车险保费合计|新能源车险保费收入|新能源车险原保险保费收入|新能源车险原保费收入|新能源车保费|新能源车业务保费|新能源车保费合计|新能源车保费收入|新能源车原保险保费收入|新能源车原保费收入|新能源車險保費|新能源車險业务保費|新能源車保費|新能源車业务保費|new energy vehicle premiums|新能源汽车保险保费|新能源车险原保费|新能源車險總保費|新能源車險佔比|新能源車險保費佔比|新能源车险总保费|新能源车险占比</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>意外伤害及健康保险保费|意健险保费|意外伤害及健康保险业务保费|意健险业务保费|意外伤害及健康保险保费合计|意健险保费合计|意外伤害及健康保险保费收入|意健险保费收入|意外伤害及健康保险原保险保费收入|意健险原保险保费收入|意外伤害及健康保险原保费收入|意健险原保费收入|意外傷害及健康保險保費|意健險保費|意外傷害及健康保險業務保費|意健險業務保費|accident &amp; health premiums|意外傷害及健康保險保費|意健險保費</t>
+          <t>意外伤害及健康保险保费|意外伤害及健康保险业务保费|意外伤害及健康保险保费合计|意外伤害及健康保险保费收入|意外伤害及健康保险原保险保费收入|意外伤害及健康保险原保费收入|意外伤害及健康险保费|意外伤害及健康险业务保费|意外伤害及健康险保费合计|意外伤害及健康险保费收入|意外伤害及健康险原保险保费收入|意外伤害及健康险原保费收入|意健险保费|意健险业务保费|意健险保费合计|意健险保费收入|意健险原保险保费收入|意健险原保费收入|意外傷害及健康保險保費|意外傷害及健康保險业务保費|意外傷害及健康險保費|意外傷害及健康險业务保費|意健險保費|意健險业务保費|accident &amp; health premiums|意外伤害和短期健康险保费|意外伤害和短期健康险业务保费|意外伤害和短期健康险保费合计|意外伤害和短期健康险保费收入|意外伤害和短期健康险原保险保费收入|意外伤害和短期健康险原保费收入|意健险保费|意健险业务保费|意健险保费合计|意健险保费收入|意健险原保险保费收入|意健险原保费收入|意外傷害和短期健康險保費|意外傷害和短期健康險业务保費|意健險保費|意健險业务保費|accident &amp; health premiums|意外及短期健康险保费|意外及短期健康险业务保费|意外及短期健康险保费合计|意外及短期健康险保费收入|意外及短期健康险原保险保费收入|意外及短期健康险原保费收入|意健险保费|意健险业务保费|意健险保费合计|意健险保费收入|意健险原保险保费收入|意健险原保费收入|意外及短期健康險保費|意外及短期健康險业务保費|意健險保費|意健險业务保費|accident &amp; health premiums|意外傷害及健康保險保費|意健險保費</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>意外伤害及健康保险保险服务收入|意健险保险服务收入|意外伤害及健康保险业务保险服务收入|意健险业务保险服务收入|意外伤害及健康保险保险服务收入合计|意健险保险服务收入合计|意外傷害及健康保險保險服務收入|意健險保險服務收入|意外傷害及健康保險業務保險服務收入|意健險業務保險服務收入|accident &amp; health insurance service revenue|意外傷害及健康保險保險服務收入|意健險保險服務收入</t>
+          <t>意外伤害及健康保险保险服务收入|意外伤害及健康保险业务保险服务收入|意外伤害及健康保险保险服务收入合计|意外伤害及健康险保险服务收入|意外伤害及健康险业务保险服务收入|意外伤害及健康险保险服务收入合计|意健险保险服务收入|意健险业务保险服务收入|意健险保险服务收入合计|意外傷害及健康保險保險服務收入|意外傷害及健康保險业务保險服務收入|意外傷害及健康險保險服務收入|意外傷害及健康險业务保險服務收入|意健險保險服務收入|意健險业务保險服務收入|accident &amp; health insurance service revenue|意外伤害和短期健康险保险服务收入|意外伤害和短期健康险业务保险服务收入|意外伤害和短期健康险保险服务收入合计|意健险保险服务收入|意健险业务保险服务收入|意健险保险服务收入合计|意外傷害和短期健康險保險服務收入|意外傷害和短期健康險业务保險服務收入|意健險保險服務收入|意健險业务保險服務收入|accident &amp; health insurance service revenue|意外及短期健康险保险服务收入|意外及短期健康险业务保险服务收入|意外及短期健康险保险服务收入合计|意健险保险服务收入|意健险业务保险服务收入|意健险保险服务收入合计|意外及短期健康險保險服務收入|意外及短期健康險业务保險服務收入|意健險保險服務收入|意健險业务保險服務收入|accident &amp; health insurance service revenue|意外傷害及健康保險保險服務收入|意健險保險服務收入</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>意外伤害及健康保险保险服务费用|意健险保险服务费用|意外伤害及健康保险业务保险服务费用|意健险业务保险服务费用|意外伤害及健康保险保险服务费用合计|意健险保险服务费用合计|意外傷害及健康保險保險服務費用|意健險保險服務費用|意外傷害及健康保險業務保險服務費用|意健險業務保險服務費用|accident &amp; health insurance service expenses|意外傷害及健康保險保險服務費用|意健險保險服務費用</t>
+          <t>意外伤害及健康保险保险服务费用|意外伤害及健康保险业务保险服务费用|意外伤害及健康保险保险服务费用合计|意外伤害及健康险保险服务费用|意外伤害及健康险业务保险服务费用|意外伤害及健康险保险服务费用合计|意健险保险服务费用|意健险业务保险服务费用|意健险保险服务费用合计|意外傷害及健康保險保險服務費用|意外傷害及健康保險业务保險服務費用|意外傷害及健康險保險服務費用|意外傷害及健康險业务保險服務費用|意健險保險服務費用|意健險业务保險服務費用|accident &amp; health insurance service expenses|意外伤害和短期健康险保险服务费用|意外伤害和短期健康险业务保险服务费用|意外伤害和短期健康险保险服务费用合计|意健险保险服务费用|意健险业务保险服务费用|意健险保险服务费用合计|意外傷害和短期健康險保險服務費用|意外傷害和短期健康險业务保險服務費用|意健險保險服務費用|意健險业务保險服務費用|accident &amp; health insurance service expenses|意外及短期健康险保险服务费用|意外及短期健康险业务保险服务费用|意外及短期健康险保险服务费用合计|意健险保险服务费用|意健险业务保险服务费用|意健险保险服务费用合计|意外及短期健康險保險服務費用|意外及短期健康險业务保險服務費用|意健險保險服務費用|意健險业务保險服務費用|accident &amp; health insurance service expenses|意外傷害及健康保險保險服務費用|意健險保險服務費用</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>意外伤害及健康保险承保利润|意健险承保利润|意外伤害及健康保险业务承保利润|意健险业务承保利润|意外傷害及健康保險承保利潤|意健險承保利潤|意外傷害及健康保險業務承保利潤|意健險業務承保利潤|accident &amp; health underwriting profit</t>
+          <t>意外伤害及健康保险承保利润|意外伤害及健康保险业务承保利润|意外伤害及健康险承保利润|意外伤害及健康险业务承保利润|意健险承保利润|意健险业务承保利润|意外傷害及健康保險承保利潤|意外傷害及健康保險业务承保利潤|意外傷害及健康險承保利潤|意外傷害及健康險业务承保利潤|意健險承保利潤|意健險业务承保利潤|accident &amp; health underwriting profit|意外伤害和短期健康险承保利润|意外伤害和短期健康险业务承保利润|意健险承保利润|意健险业务承保利润|意外傷害和短期健康險承保利潤|意外傷害和短期健康險业务承保利潤|意健險承保利潤|意健險业务承保利潤|accident &amp; health underwriting profit|意外及短期健康险承保利润|意外及短期健康险业务承保利润|意健险承保利润|意健险业务承保利润|意外及短期健康險承保利潤|意外及短期健康險业务承保利潤|意健險承保利潤|意健險业务承保利潤|accident &amp; health underwriting profit</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>意外伤害及健康保险综合成本率|意健险综合成本率|意外伤害及健康保险业务综合成本率|意健险业务综合成本率|意外傷害及健康保險綜合成本率|意健險綜合成本率|意外傷害及健康保險業務綜合成本率|意健險業務綜合成本率|accident &amp; health combined ratio</t>
+          <t>意外伤害及健康保险综合成本率|意外伤害及健康保险业务综合成本率|意外伤害及健康险综合成本率|意外伤害及健康险业务综合成本率|意健险综合成本率|意健险业务综合成本率|意外傷害及健康保險綜合成本率|意外傷害及健康保險业务綜合成本率|意外傷害及健康險綜合成本率|意外傷害及健康險业务綜合成本率|意健險綜合成本率|意健險业务綜合成本率|accident &amp; health combined ratio|意外伤害和短期健康险综合成本率|意外伤害和短期健康险业务综合成本率|意健险综合成本率|意健险业务综合成本率|意外傷害和短期健康險綜合成本率|意外傷害和短期健康險业务綜合成本率|意健險綜合成本率|意健險业务綜合成本率|accident &amp; health combined ratio|意外及短期健康险综合成本率|意外及短期健康险业务综合成本率|意健险综合成本率|意健险业务综合成本率|意外及短期健康險綜合成本率|意外及短期健康險业务綜合成本率|意健險綜合成本率|意健險业务綜合成本率|accident &amp; health combined ratio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>车险承保利润|机动车辆保险承保利润|车险业务承保利润|机动车辆保险业务承保利润|車險承保利潤|機動車輛保險承保利潤|車險業務承保利潤|機動車輛保險業務承保利潤|motor underwriting profit|车险承保经营利润|机动车辆保险承保经营利润</t>
+          <t>车险承保利润|车险业务承保利润|机动车辆保险承保利润|机动车辆保险业务承保利润|机动车辆险承保利润|机动车辆险业务承保利润|車險承保利潤|車險业务承保利潤|機動車輛保險承保利潤|機動車輛保險业务承保利潤|機動車輛險承保利潤|機動車輛險业务承保利潤|motor underwriting profit|车险承保经营利润|机动车辆保险承保经营利润</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>非车险承保利润|非机动车辆保险承保利润|非车险业务承保利润|非机动车辆保险业务承保利润|非車險承保利潤|非機動車輛保險承保利潤|非車險業務承保利潤|非機動車輛保險業務承保利潤|non-motor underwriting profit|非车险承保经营利润|非机动车辆保险承保经营利润</t>
+          <t>非车险承保利润|非车险业务承保利润|非机动车辆保险承保利润|非机动车辆保险业务承保利润|非机动车辆险承保利润|非机动车辆险业务承保利润|非車險承保利潤|非車險业务承保利潤|非機動車輛保險承保利潤|非機動車輛保險业务承保利潤|非機動車輛險承保利潤|非機動車輛險业务承保利潤|non-motor underwriting profit|非车险承保经营利润|非机动车辆保险承保经营利润</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>农业保险承保利润|农险承保利润|农业保险业务承保利润|农险业务承保利润|農業保險承保利潤|農險承保利潤|農業保險業務承保利潤|農險業務承保利潤|agricultural underwriting profit|农业保险承保经营利润|农险承保经营利润</t>
+          <t>农业保险承保利润|农业保险业务承保利润|农业险承保利润|农业险业务承保利润|农险承保利润|农险业务承保利润|農業保險承保利潤|農業保險业务承保利潤|農業險承保利潤|農業險业务承保利潤|農險承保利潤|農險业务承保利潤|agricultural underwriting profit|农业保险承保经营利润|农险承保经营利润</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>健康险承保利润|健康保险承保利润|健康险业务承保利润|健康保险业务承保利润|健康險承保利潤|健康保險承保利潤|健康險業務承保利潤|健康保險業務承保利潤|health underwriting profit|健康险承保经营利润|健康保险承保经营利润</t>
+          <t>健康险承保利润|健康险业务承保利润|健康保险承保利润|健康保险业务承保利润|健康险承保利润|健康险业务承保利润|健康險承保利潤|健康險业务承保利潤|健康保險承保利潤|健康保險业务承保利潤|健康險承保利潤|健康險业务承保利潤|health underwriting profit|健康险承保经营利润|健康保险承保经营利润</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>责任保险承保利润|责任险承保利润|责任保险业务承保利润|责任险业务承保利润|責任保險承保利潤|責任險承保利潤|責任保險業務承保利潤|責任險業務承保利潤|liability underwriting profit|责任保险承保经营利润|责任险承保经营利润</t>
+          <t>责任保险承保利润|责任保险业务承保利润|责任险承保利润|责任险业务承保利润|责任险承保利润|责任险业务承保利润|責任保險承保利潤|責任保險业务承保利潤|責任險承保利潤|責任險业务承保利潤|責任險承保利潤|責任險业务承保利潤|liability underwriting profit|责任保险承保经营利润|责任险承保经营利润</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>意外伤害保险承保利润|意外险承保利润|意外伤害保险业务承保利润|意外险业务承保利润|意外傷害保險承保利潤|意外險承保利潤|意外傷害保險業務承保利潤|意外險業務承保利潤|accident underwriting profit|意外伤害保险承保经营利润|意外险承保经营利润</t>
+          <t>意外伤害保险承保利润|意外伤害保险业务承保利润|意外伤害险承保利润|意外伤害险业务承保利润|意外险承保利润|意外险业务承保利润|意外傷害保險承保利潤|意外傷害保險业务承保利潤|意外傷害險承保利潤|意外傷害險业务承保利潤|意外險承保利潤|意外險业务承保利潤|accident underwriting profit|意外伤害保险承保经营利润|意外险承保经营利润</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>企业财产保险承保利润|企财险承保利润|企业财产保险业务承保利润|企财险业务承保利润|企業財產保險承保利潤|企財險承保利潤|企業財產保險業務承保利潤|企財險業務承保利潤|commercial property underwriting profit|企业财产保险承保经营利润|企财险承保经营利润</t>
+          <t>企业财产保险承保利润|企业财产保险业务承保利润|企业财产险承保利润|企业财产险业务承保利润|企财险承保利润|企财险业务承保利润|企業財產保險承保利潤|企業財產保險业务承保利潤|企業財產險承保利潤|企業財產險业务承保利潤|企財險承保利潤|企財險业务承保利潤|commercial property underwriting profit|企业财产保险承保经营利润|企财险承保经营利润</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>保证保险承保利润|保证险承保利润|保证保险业务承保利润|保证险业务承保利润|保證保險承保利潤|保證險承保利潤|保證保險業務承保利潤|保證險業務承保利潤|guarantee underwriting profit|保证保险承保经营利润|保证险承保经营利润</t>
+          <t>保证保险承保利润|保证保险业务承保利润|保证险承保利润|保证险业务承保利润|保证险承保利润|保证险业务承保利润|保證保險承保利潤|保證保險业务承保利潤|保證險承保利潤|保證險业务承保利潤|保證險承保利潤|保證險业务承保利潤|guarantee underwriting profit|保证保险承保经营利润|保证险承保经营利润</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>货物运输保险承保利润|货运险承保利润|货物运输保险业务承保利润|货运险业务承保利润|貨物運輸保險承保利潤|貨運險承保利潤|貨物運輸保險業務承保利潤|貨運險業務承保利潤|cargo transportation underwriting profit|货物运输保险承保经营利润|货运险承保经营利润</t>
+          <t>货物运输保险承保利润|货物运输保险业务承保利润|货物运输险承保利润|货物运输险业务承保利润|货运险承保利润|货运险业务承保利润|貨物運輸保險承保利潤|貨物運輸保險业务承保利潤|貨物運輸險承保利潤|貨物運輸險业务承保利潤|貨運險承保利潤|貨運險业务承保利潤|cargo transportation underwriting profit|货物运输保险承保经营利润|货运险承保经营利润</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>新能源车险承保利润|新能源车承保利润|新能源车险业务承保利润|新能源车业务承保利润|新能源車險承保利潤|新能源車承保利潤|新能源車險業務承保利潤|新能源車業務承保利潤|new energy vehicle underwriting profit|新能源车险承保经营利润|新能源车承保经营利润</t>
+          <t>新能源车险承保利润|新能源车险业务承保利润|新能源车承保利润|新能源车业务承保利润|新能源車險承保利潤|新能源車險业务承保利潤|新能源車承保利潤|新能源車业务承保利潤|new energy vehicle underwriting profit|新能源车险承保经营利润|新能源车承保经营利润</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>农业保险综合成本率|农险综合成本率|农业保险业务综合成本率|农险业务综合成本率|農業保險綜合成本率|農險綜合成本率|農業保險業務綜合成本率|農險業務綜合成本率|agricultural combined ratio|农业保险COR|农险COR|农业保险承保综合成本率|农险承保综合成本率</t>
+          <t>农业保险综合成本率|农业保险业务综合成本率|农业险综合成本率|农业险业务综合成本率|农险综合成本率|农险业务综合成本率|農業保險綜合成本率|農業保險业务綜合成本率|農業險綜合成本率|農業險业务綜合成本率|農險綜合成本率|農險业务綜合成本率|agricultural combined ratio|农业保险COR|农险COR|农业保险承保综合成本率|农险承保综合成本率</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>健康险综合成本率|健康保险综合成本率|健康险业务综合成本率|健康保险业务综合成本率|健康險綜合成本率|健康保險綜合成本率|健康險業務綜合成本率|健康保險業務綜合成本率|health combined ratio|健康险COR|健康保险COR|健康险承保综合成本率|健康保险承保综合成本率</t>
+          <t>健康险综合成本率|健康险业务综合成本率|健康保险综合成本率|健康保险业务综合成本率|健康险综合成本率|健康险业务综合成本率|健康險綜合成本率|健康險业务綜合成本率|健康保險綜合成本率|健康保險业务綜合成本率|健康險綜合成本率|健康險业务綜合成本率|health combined ratio|健康险COR|健康保险COR|健康险承保综合成本率|健康保险承保综合成本率</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>责任保险综合成本率|责任险综合成本率|责任保险业务综合成本率|责任险业务综合成本率|責任保險綜合成本率|責任險綜合成本率|責任保險業務綜合成本率|責任險業務綜合成本率|liability combined ratio|责任保险COR|责任险COR|责任保险承保综合成本率|责任险承保综合成本率</t>
+          <t>责任保险综合成本率|责任保险业务综合成本率|责任险综合成本率|责任险业务综合成本率|责任险综合成本率|责任险业务综合成本率|責任保險綜合成本率|責任保險业务綜合成本率|責任險綜合成本率|責任險业务綜合成本率|責任險綜合成本率|責任險业务綜合成本率|liability combined ratio|责任保险COR|责任险COR|责任保险承保综合成本率|责任险承保综合成本率</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>意外伤害保险综合成本率|意外险综合成本率|意外伤害保险业务综合成本率|意外险业务综合成本率|意外傷害保險綜合成本率|意外險綜合成本率|意外傷害保險業務綜合成本率|意外險業務綜合成本率|accident combined ratio|意外伤害保险COR|意外险COR|意外伤害保险承保综合成本率|意外险承保综合成本率</t>
+          <t>意外伤害保险综合成本率|意外伤害保险业务综合成本率|意外伤害险综合成本率|意外伤害险业务综合成本率|意外险综合成本率|意外险业务综合成本率|意外傷害保險綜合成本率|意外傷害保險业务綜合成本率|意外傷害險綜合成本率|意外傷害險业务綜合成本率|意外險綜合成本率|意外險业务綜合成本率|accident combined ratio|意外伤害保险COR|意外险COR|意外伤害保险承保综合成本率|意外险承保综合成本率</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>企业财产保险综合成本率|企财险综合成本率|企业财产保险业务综合成本率|企财险业务综合成本率|企業財產保險綜合成本率|企財險綜合成本率|企業財產保險業務綜合成本率|企財險業務綜合成本率|commercial property combined ratio|企业财产保险COR|企财险COR|企业财产保险承保综合成本率|企财险承保综合成本率</t>
+          <t>企业财产保险综合成本率|企业财产保险业务综合成本率|企业财产险综合成本率|企业财产险业务综合成本率|企财险综合成本率|企财险业务综合成本率|企業財產保險綜合成本率|企業財產保險业务綜合成本率|企業財產險綜合成本率|企業財產險业务綜合成本率|企財險綜合成本率|企財險业务綜合成本率|commercial property combined ratio|企业财产保险COR|企财险COR|企业财产保险承保综合成本率|企财险承保综合成本率</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>保证保险综合成本率|保证险综合成本率|保证保险业务综合成本率|保证险业务综合成本率|保證保險綜合成本率|保證險綜合成本率|保證保險業務綜合成本率|保證險業務綜合成本率|guarantee combined ratio|保证保险COR|保证险COR|保证保险承保综合成本率|保证险承保综合成本率</t>
+          <t>保证保险综合成本率|保证保险业务综合成本率|保证险综合成本率|保证险业务综合成本率|保证险综合成本率|保证险业务综合成本率|保證保險綜合成本率|保證保險业务綜合成本率|保證險綜合成本率|保證險业务綜合成本率|保證險綜合成本率|保證險业务綜合成本率|guarantee combined ratio|保证保险COR|保证险COR|保证保险承保综合成本率|保证险承保综合成本率</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>货物运输保险综合成本率|货运险综合成本率|货物运输保险业务综合成本率|货运险业务综合成本率|貨物運輸保險綜合成本率|貨運險綜合成本率|貨物運輸保險業務綜合成本率|貨運險業務綜合成本率|cargo transportation combined ratio|货物运输保险COR|货运险COR|货物运输保险承保综合成本率|货运险承保综合成本率</t>
+          <t>货物运输保险综合成本率|货物运输保险业务综合成本率|货物运输险综合成本率|货物运输险业务综合成本率|货运险综合成本率|货运险业务综合成本率|貨物運輸保險綜合成本率|貨物運輸保險业务綜合成本率|貨物運輸險綜合成本率|貨物運輸險业务綜合成本率|貨運險綜合成本率|貨運險业务綜合成本率|cargo transportation combined ratio|货物运输保险COR|货运险COR|货物运输保险承保综合成本率|货运险承保综合成本率</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>新能源车险综合成本率|新能源车综合成本率|新能源车险业务综合成本率|新能源车业务综合成本率|新能源車險綜合成本率|新能源車綜合成本率|新能源車險業務綜合成本率|新能源車業務綜合成本率|new energy vehicle combined ratio|新能源车险COR|新能源车COR|新能源车险承保综合成本率|新能源车承保综合成本率</t>
+          <t>新能源车险综合成本率|新能源车险业务综合成本率|新能源车综合成本率|新能源车业务综合成本率|新能源車險綜合成本率|新能源車險业务綜合成本率|新能源車綜合成本率|新能源車业务綜合成本率|new energy vehicle combined ratio|新能源车险COR|新能源车COR|新能源车险承保综合成本率|新能源车承保综合成本率</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
